--- a/resources/M678/spc_cpk_detail.xlsx
+++ b/resources/M678/spc_cpk_detail.xlsx
@@ -978,10 +978,10 @@
         <v>46230.08362268518</v>
       </c>
       <c r="J3">
-        <v>1.773962199259438</v>
+        <v>1.773962199259439</v>
       </c>
       <c r="K3">
-        <v>1.773962199259438</v>
+        <v>1.773962199259439</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2413,10 +2413,10 @@
         <v>46180.63209490741</v>
       </c>
       <c r="J44">
-        <v>2.26628616499949</v>
+        <v>2.266286164999491</v>
       </c>
       <c r="K44">
-        <v>2.26628616499949</v>
+        <v>2.266286164999491</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2588,10 +2588,10 @@
         <v>46219.1537962963</v>
       </c>
       <c r="J49">
-        <v>2.282197207180397</v>
+        <v>2.282197207180398</v>
       </c>
       <c r="K49">
-        <v>2.282197207180397</v>
+        <v>2.282197207180398</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3218,10 +3218,10 @@
         <v>46180.63209490741</v>
       </c>
       <c r="J67">
-        <v>2.150602611916161</v>
+        <v>2.150602611916162</v>
       </c>
       <c r="K67">
-        <v>2.150602611916161</v>
+        <v>2.150602611916162</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3428,10 +3428,10 @@
         <v>46229.69837962963</v>
       </c>
       <c r="J73">
-        <v>2.40153374222208</v>
+        <v>2.401533742222081</v>
       </c>
       <c r="K73">
-        <v>2.40153374222208</v>
+        <v>2.401533742222081</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3918,10 +3918,10 @@
         <v>46229.69837962963</v>
       </c>
       <c r="J87">
-        <v>2.40153374222208</v>
+        <v>2.401533742222081</v>
       </c>
       <c r="K87">
-        <v>2.40153374222208</v>
+        <v>2.401533742222081</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -5248,10 +5248,10 @@
         <v>46218.5697337963</v>
       </c>
       <c r="J125">
-        <v>2.222105311446572</v>
+        <v>2.222105311446571</v>
       </c>
       <c r="K125">
-        <v>2.222105311446572</v>
+        <v>2.222105311446571</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5843,10 +5843,10 @@
         <v>46221.5037962963</v>
       </c>
       <c r="J142">
-        <v>2.226603617143894</v>
+        <v>2.226603617143895</v>
       </c>
       <c r="K142">
-        <v>2.226603617143894</v>
+        <v>2.226603617143895</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5983,10 +5983,10 @@
         <v>46187.98627314815</v>
       </c>
       <c r="J146">
-        <v>2.100473496293771</v>
+        <v>2.100473496293772</v>
       </c>
       <c r="K146">
-        <v>2.100473496293771</v>
+        <v>2.100473496293772</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -6088,10 +6088,10 @@
         <v>46221.5037962963</v>
       </c>
       <c r="J149">
-        <v>2.226603617143894</v>
+        <v>2.226603617143895</v>
       </c>
       <c r="K149">
-        <v>2.226603617143894</v>
+        <v>2.226603617143895</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -7838,10 +7838,10 @@
         <v>46202.29263888889</v>
       </c>
       <c r="J199">
-        <v>1.671470011463279</v>
+        <v>1.67147001146328</v>
       </c>
       <c r="K199">
-        <v>1.671470011463279</v>
+        <v>1.67147001146328</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -7943,10 +7943,10 @@
         <v>46182.90564814815</v>
       </c>
       <c r="J202">
-        <v>2.431505375977241</v>
+        <v>2.43150537597724</v>
       </c>
       <c r="K202">
-        <v>2.431505375977241</v>
+        <v>2.43150537597724</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -8188,10 +8188,10 @@
         <v>46202.29263888889</v>
       </c>
       <c r="J209">
-        <v>1.671470011463279</v>
+        <v>1.67147001146328</v>
       </c>
       <c r="K209">
-        <v>1.671470011463279</v>
+        <v>1.67147001146328</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -8258,10 +8258,10 @@
         <v>46222.496875</v>
       </c>
       <c r="J211">
-        <v>2.196024843797816</v>
+        <v>2.196024843797817</v>
       </c>
       <c r="K211">
-        <v>2.196024843797816</v>
+        <v>2.196024843797817</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -9553,10 +9553,10 @@
         <v>46227.10450231482</v>
       </c>
       <c r="J248">
-        <v>1.836180969760491</v>
+        <v>1.83618096976049</v>
       </c>
       <c r="K248">
-        <v>1.836180969760491</v>
+        <v>1.83618096976049</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -9763,10 +9763,10 @@
         <v>46184.85471064815</v>
       </c>
       <c r="J254">
-        <v>2.440979194210679</v>
+        <v>2.440979194210678</v>
       </c>
       <c r="K254">
-        <v>2.440979194210679</v>
+        <v>2.440979194210678</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -9833,10 +9833,10 @@
         <v>46188.09811342593</v>
       </c>
       <c r="J256">
-        <v>1.665888814310093</v>
+        <v>1.665888814310094</v>
       </c>
       <c r="K256">
-        <v>1.665888814310093</v>
+        <v>1.665888814310094</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -12843,10 +12843,10 @@
         <v>46228.39672453704</v>
       </c>
       <c r="J342">
-        <v>3.808107612980759</v>
+        <v>3.80810761298076</v>
       </c>
       <c r="K342">
-        <v>3.808107612980759</v>
+        <v>3.80810761298076</v>
       </c>
     </row>
     <row r="343" spans="1:11">
@@ -13123,10 +13123,10 @@
         <v>46230.02590277778</v>
       </c>
       <c r="J350">
-        <v>4.36691311681581</v>
+        <v>4.366913116815809</v>
       </c>
       <c r="K350">
-        <v>4.36691311681581</v>
+        <v>4.366913116815809</v>
       </c>
     </row>
     <row r="351" spans="1:11">
@@ -13426,10 +13426,10 @@
         <v>46230.02590277778</v>
       </c>
       <c r="J359">
-        <v>4.36691311681581</v>
+        <v>4.366913116815809</v>
       </c>
       <c r="K359">
-        <v>4.36691311681581</v>
+        <v>4.366913116815809</v>
       </c>
     </row>
     <row r="360" spans="1:11">
@@ -13846,10 +13846,10 @@
         <v>46224.98856481481</v>
       </c>
       <c r="J371">
-        <v>0.7872217677221375</v>
+        <v>0.7872217677221376</v>
       </c>
       <c r="K371">
-        <v>0.7872217677221375</v>
+        <v>0.7872217677221376</v>
       </c>
     </row>
     <row r="372" spans="1:11">
@@ -14126,10 +14126,10 @@
         <v>46188.33339120371</v>
       </c>
       <c r="J379">
-        <v>1.642796240892491</v>
+        <v>1.64279624089249</v>
       </c>
       <c r="K379">
-        <v>1.642796240892491</v>
+        <v>1.64279624089249</v>
       </c>
     </row>
     <row r="380" spans="1:11">
@@ -14301,10 +14301,10 @@
         <v>46188.33339120371</v>
       </c>
       <c r="J384">
-        <v>1.642796240892491</v>
+        <v>1.64279624089249</v>
       </c>
       <c r="K384">
-        <v>1.642796240892491</v>
+        <v>1.64279624089249</v>
       </c>
     </row>
     <row r="385" spans="1:11">
@@ -14919,10 +14919,10 @@
         <v>46202.99149305555</v>
       </c>
       <c r="J402">
-        <v>1.911725319522703</v>
+        <v>1.911725319522704</v>
       </c>
       <c r="K402">
-        <v>1.911725319522703</v>
+        <v>1.911725319522704</v>
       </c>
     </row>
     <row r="403" spans="1:11">
@@ -15129,10 +15129,10 @@
         <v>46193.3550925926</v>
       </c>
       <c r="J408">
-        <v>1.320587017227386</v>
+        <v>1.320587017227385</v>
       </c>
       <c r="K408">
-        <v>1.320587017227386</v>
+        <v>1.320587017227385</v>
       </c>
     </row>
     <row r="409" spans="1:11">
@@ -15479,10 +15479,10 @@
         <v>46203.39335648148</v>
       </c>
       <c r="J418">
-        <v>1.397489970518077</v>
+        <v>1.397489970518076</v>
       </c>
       <c r="K418">
-        <v>1.397489970518077</v>
+        <v>1.397489970518076</v>
       </c>
     </row>
     <row r="419" spans="1:11">
@@ -15759,10 +15759,10 @@
         <v>46230.84887731481</v>
       </c>
       <c r="J426">
-        <v>2.259408333459664</v>
+        <v>2.412948918768807</v>
       </c>
       <c r="K426">
-        <v>2.259408333459664</v>
+        <v>2.412948918768807</v>
       </c>
     </row>
     <row r="427" spans="1:11">
@@ -15934,10 +15934,10 @@
         <v>46230.84887731481</v>
       </c>
       <c r="J431">
-        <v>1.821067772230513</v>
+        <v>2.249540311011659</v>
       </c>
       <c r="K431">
-        <v>1.821067772230513</v>
+        <v>2.249540311011659</v>
       </c>
     </row>
     <row r="432" spans="1:11">
@@ -16284,10 +16284,10 @@
         <v>46227.19659722222</v>
       </c>
       <c r="J441">
-        <v>41.36093961397549</v>
+        <v>41.36093961397548</v>
       </c>
       <c r="K441">
-        <v>41.36093961397549</v>
+        <v>41.36093961397548</v>
       </c>
     </row>
     <row r="442" spans="1:11">
@@ -16354,10 +16354,10 @@
         <v>46230.84887731481</v>
       </c>
       <c r="J443">
-        <v>1.821067772230513</v>
+        <v>2.249540311011659</v>
       </c>
       <c r="K443">
-        <v>1.821067772230513</v>
+        <v>2.249540311011659</v>
       </c>
     </row>
     <row r="444" spans="1:11">
@@ -16424,10 +16424,10 @@
         <v>46230.81168981481</v>
       </c>
       <c r="J445">
-        <v>2.411926705447249</v>
+        <v>2.470368645120348</v>
       </c>
       <c r="K445">
-        <v>2.411926705447249</v>
+        <v>2.470368645120348</v>
       </c>
     </row>
     <row r="446" spans="1:11">
@@ -16494,10 +16494,10 @@
         <v>46207.54465277777</v>
       </c>
       <c r="J447">
-        <v>2.487511037448469</v>
+        <v>2.48751103744847</v>
       </c>
       <c r="K447">
-        <v>2.487511037448469</v>
+        <v>2.48751103744847</v>
       </c>
     </row>
     <row r="448" spans="1:11">
@@ -16529,10 +16529,10 @@
         <v>46230.81168981481</v>
       </c>
       <c r="J448">
-        <v>2.500844546948326</v>
+        <v>2.448838456844251</v>
       </c>
       <c r="K448">
-        <v>2.500844546948326</v>
+        <v>2.448838456844251</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -16564,10 +16564,10 @@
         <v>46191.07377314815</v>
       </c>
       <c r="J449">
-        <v>2.390138496580181</v>
+        <v>2.390138496580182</v>
       </c>
       <c r="K449">
-        <v>2.390138496580181</v>
+        <v>2.390138496580182</v>
       </c>
     </row>
     <row r="450" spans="1:11">
@@ -16634,10 +16634,10 @@
         <v>46207.54465277777</v>
       </c>
       <c r="J451">
-        <v>2.487511037448469</v>
+        <v>2.48751103744847</v>
       </c>
       <c r="K451">
-        <v>2.487511037448469</v>
+        <v>2.48751103744847</v>
       </c>
     </row>
     <row r="452" spans="1:11">
@@ -16669,10 +16669,10 @@
         <v>46230.81168981481</v>
       </c>
       <c r="J452">
-        <v>2.500844546948326</v>
+        <v>2.448838456844251</v>
       </c>
       <c r="K452">
-        <v>2.500844546948326</v>
+        <v>2.448838456844251</v>
       </c>
     </row>
     <row r="453" spans="1:11">
@@ -16739,10 +16739,10 @@
         <v>46213.1653125</v>
       </c>
       <c r="J454">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
       <c r="K454">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
     </row>
     <row r="455" spans="1:11">
@@ -16809,10 +16809,10 @@
         <v>46213.1653125</v>
       </c>
       <c r="J456">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
       <c r="K456">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
     </row>
     <row r="457" spans="1:11">
@@ -16914,10 +16914,10 @@
         <v>46213.1653125</v>
       </c>
       <c r="J459">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
       <c r="K459">
-        <v>1.932714689851709</v>
+        <v>1.932714689851708</v>
       </c>
     </row>
     <row r="460" spans="1:11">
@@ -18174,10 +18174,10 @@
         <v>46200.23240740741</v>
       </c>
       <c r="J495">
-        <v>1.830025979532591</v>
+        <v>1.830025979532592</v>
       </c>
       <c r="K495">
-        <v>1.830025979532591</v>
+        <v>1.830025979532592</v>
       </c>
     </row>
     <row r="496" spans="1:11">
@@ -18489,10 +18489,10 @@
         <v>46200.26049768519</v>
       </c>
       <c r="J504">
-        <v>1.66479641536668</v>
+        <v>1.664796415366681</v>
       </c>
       <c r="K504">
-        <v>1.66479641536668</v>
+        <v>1.664796415366681</v>
       </c>
     </row>
     <row r="505" spans="1:11">
@@ -19504,10 +19504,10 @@
         <v>46196.87370370371</v>
       </c>
       <c r="J533">
-        <v>1.31285283116541</v>
+        <v>1.312852831165411</v>
       </c>
       <c r="K533">
-        <v>1.31285283116541</v>
+        <v>1.312852831165411</v>
       </c>
     </row>
     <row r="534" spans="1:11">
@@ -20099,10 +20099,10 @@
         <v>46201.03612268518</v>
       </c>
       <c r="J550">
-        <v>1.533136654933763</v>
+        <v>1.533136654933762</v>
       </c>
       <c r="K550">
-        <v>1.533136654933763</v>
+        <v>1.533136654933762</v>
       </c>
     </row>
     <row r="551" spans="1:11">
@@ -20169,10 +20169,10 @@
         <v>46201.03612268518</v>
       </c>
       <c r="J552">
-        <v>1.533136654933763</v>
+        <v>1.533136654933762</v>
       </c>
       <c r="K552">
-        <v>1.533136654933763</v>
+        <v>1.533136654933762</v>
       </c>
     </row>
     <row r="553" spans="1:11">
@@ -20274,10 +20274,10 @@
         <v>46200.99974537037</v>
       </c>
       <c r="J555">
-        <v>1.702925994369464</v>
+        <v>1.702925994369463</v>
       </c>
       <c r="K555">
-        <v>1.702925994369464</v>
+        <v>1.702925994369463</v>
       </c>
     </row>
     <row r="556" spans="1:11">
@@ -21499,10 +21499,10 @@
         <v>46212.10982638889</v>
       </c>
       <c r="J590">
-        <v>1.563919514780964</v>
+        <v>1.563919514780963</v>
       </c>
       <c r="K590">
-        <v>1.563919514780964</v>
+        <v>1.563919514780963</v>
       </c>
     </row>
     <row r="591" spans="1:11">
@@ -23389,10 +23389,10 @@
         <v>46214.02072916667</v>
       </c>
       <c r="J644">
-        <v>1.282686666614346</v>
+        <v>1.282686666614345</v>
       </c>
       <c r="K644">
-        <v>1.282686666614346</v>
+        <v>1.282686666614345</v>
       </c>
     </row>
     <row r="645" spans="1:11">
@@ -23529,10 +23529,10 @@
         <v>46203.68648148148</v>
       </c>
       <c r="J648">
-        <v>1.07507023493576</v>
+        <v>1.075070234935759</v>
       </c>
       <c r="K648">
-        <v>1.07507023493576</v>
+        <v>1.075070234935759</v>
       </c>
     </row>
     <row r="649" spans="1:11">
@@ -23634,10 +23634,10 @@
         <v>46214.02072916667</v>
       </c>
       <c r="J651">
-        <v>1.282686666614346</v>
+        <v>1.282686666614345</v>
       </c>
       <c r="K651">
-        <v>1.282686666614346</v>
+        <v>1.282686666614345</v>
       </c>
     </row>
     <row r="652" spans="1:11">
@@ -24614,10 +24614,10 @@
         <v>46207.47296296297</v>
       </c>
       <c r="J679">
-        <v>1.871024613505987</v>
+        <v>1.871024613505986</v>
       </c>
       <c r="K679">
-        <v>1.871024613505987</v>
+        <v>1.871024613505986</v>
       </c>
     </row>
     <row r="680" spans="1:11">
@@ -24964,10 +24964,10 @@
         <v>46219.29641203704</v>
       </c>
       <c r="J689">
-        <v>2.046634089418822</v>
+        <v>2.046634089418823</v>
       </c>
       <c r="K689">
-        <v>2.046634089418822</v>
+        <v>2.046634089418823</v>
       </c>
     </row>
     <row r="690" spans="1:11">
@@ -25139,10 +25139,10 @@
         <v>46200.1355787037</v>
       </c>
       <c r="J694">
-        <v>2.087687739652189</v>
+        <v>2.087687739652188</v>
       </c>
       <c r="K694">
-        <v>2.087687739652189</v>
+        <v>2.087687739652188</v>
       </c>
     </row>
     <row r="695" spans="1:11">
@@ -25349,10 +25349,10 @@
         <v>46219.29641203704</v>
       </c>
       <c r="J700">
-        <v>2.046634089418822</v>
+        <v>2.046634089418823</v>
       </c>
       <c r="K700">
-        <v>2.046634089418822</v>
+        <v>2.046634089418823</v>
       </c>
     </row>
     <row r="701" spans="1:11">
@@ -25909,10 +25909,10 @@
         <v>46208.56366898148</v>
       </c>
       <c r="J716">
-        <v>1.999453335585944</v>
+        <v>1.999453335585943</v>
       </c>
       <c r="K716">
-        <v>1.999453335585944</v>
+        <v>1.999453335585943</v>
       </c>
     </row>
     <row r="717" spans="1:11">
@@ -26014,10 +26014,10 @@
         <v>46203.1275</v>
       </c>
       <c r="J719">
-        <v>1.945808840490073</v>
+        <v>1.945808840490074</v>
       </c>
       <c r="K719">
-        <v>1.945808840490073</v>
+        <v>1.945808840490074</v>
       </c>
     </row>
     <row r="720" spans="1:11">
@@ -26294,10 +26294,10 @@
         <v>46176.85627314815</v>
       </c>
       <c r="J727">
-        <v>2.460064168404347</v>
+        <v>2.460064168404348</v>
       </c>
       <c r="K727">
-        <v>2.460064168404347</v>
+        <v>2.460064168404348</v>
       </c>
     </row>
     <row r="728" spans="1:11">
@@ -26364,10 +26364,10 @@
         <v>46199.99631944444</v>
       </c>
       <c r="J729">
-        <v>2.506740234766664</v>
+        <v>2.506740234766663</v>
       </c>
       <c r="K729">
-        <v>2.506740234766664</v>
+        <v>2.506740234766663</v>
       </c>
     </row>
     <row r="730" spans="1:11">
@@ -27134,10 +27134,10 @@
         <v>46207.47296296297</v>
       </c>
       <c r="J751">
-        <v>1.5323995516083</v>
+        <v>1.532399551608301</v>
       </c>
       <c r="K751">
-        <v>1.5323995516083</v>
+        <v>1.532399551608301</v>
       </c>
     </row>
     <row r="752" spans="1:11">
@@ -27729,10 +27729,10 @@
         <v>46203.1275</v>
       </c>
       <c r="J768">
-        <v>2.371781687200063</v>
+        <v>2.371781687200064</v>
       </c>
       <c r="K768">
-        <v>2.371781687200063</v>
+        <v>2.371781687200064</v>
       </c>
     </row>
     <row r="769" spans="1:11">
@@ -30914,10 +30914,10 @@
         <v>46184.62703703704</v>
       </c>
       <c r="J859">
-        <v>1.337915282474242</v>
+        <v>1.337915282474243</v>
       </c>
       <c r="K859">
-        <v>1.337915282474242</v>
+        <v>1.337915282474243</v>
       </c>
     </row>
     <row r="860" spans="1:11">
@@ -31824,10 +31824,10 @@
         <v>46182.40030092592</v>
       </c>
       <c r="J885">
-        <v>1.813381373525868</v>
+        <v>1.813381373525867</v>
       </c>
       <c r="K885">
-        <v>1.813381373525868</v>
+        <v>1.813381373525867</v>
       </c>
     </row>
     <row r="886" spans="1:11">
@@ -32174,10 +32174,10 @@
         <v>46198.25758101852</v>
       </c>
       <c r="J895">
-        <v>1.742366345067584</v>
+        <v>1.742366345067585</v>
       </c>
       <c r="K895">
-        <v>1.742366345067584</v>
+        <v>1.742366345067585</v>
       </c>
     </row>
     <row r="896" spans="1:11">
@@ -34688,10 +34688,10 @@
         <v>46220.30376157408</v>
       </c>
       <c r="J967">
-        <v>2.949972954209134</v>
+        <v>2.949972954209135</v>
       </c>
       <c r="K967">
-        <v>2.949972954209134</v>
+        <v>2.949972954209135</v>
       </c>
     </row>
     <row r="968" spans="1:11">
@@ -35738,10 +35738,10 @@
         <v>46202.41592592592</v>
       </c>
       <c r="J997">
-        <v>1.45345065788376</v>
+        <v>1.453450657883761</v>
       </c>
       <c r="K997">
-        <v>1.45345065788376</v>
+        <v>1.453450657883761</v>
       </c>
     </row>
     <row r="998" spans="1:11">
@@ -35948,10 +35948,10 @@
         <v>46202.41592592592</v>
       </c>
       <c r="J1003">
-        <v>1.45345065788376</v>
+        <v>1.453450657883761</v>
       </c>
       <c r="K1003">
-        <v>1.45345065788376</v>
+        <v>1.453450657883761</v>
       </c>
     </row>
     <row r="1004" spans="1:11">
@@ -36158,10 +36158,10 @@
         <v>46183.41065972222</v>
       </c>
       <c r="J1009">
-        <v>5.292702472023204</v>
+        <v>5.292702472023203</v>
       </c>
       <c r="K1009">
-        <v>5.292702472023204</v>
+        <v>5.292702472023203</v>
       </c>
     </row>
     <row r="1010" spans="1:11">
@@ -36368,10 +36368,10 @@
         <v>46177.18960648148</v>
       </c>
       <c r="J1015">
-        <v>3.635607433344905</v>
+        <v>3.635607433344904</v>
       </c>
       <c r="K1015">
-        <v>3.635607433344905</v>
+        <v>3.635607433344904</v>
       </c>
     </row>
     <row r="1016" spans="1:11">
@@ -36473,10 +36473,10 @@
         <v>46183.41065972222</v>
       </c>
       <c r="J1018">
-        <v>5.292702472023204</v>
+        <v>5.292702472023203</v>
       </c>
       <c r="K1018">
-        <v>5.292702472023204</v>
+        <v>5.292702472023203</v>
       </c>
     </row>
     <row r="1019" spans="1:11">
@@ -36613,10 +36613,10 @@
         <v>46209.95994212963</v>
       </c>
       <c r="J1022">
-        <v>2.328137100925356</v>
+        <v>2.328137100925357</v>
       </c>
       <c r="K1022">
-        <v>2.328137100925356</v>
+        <v>2.328137100925357</v>
       </c>
     </row>
     <row r="1023" spans="1:11">
@@ -36823,10 +36823,10 @@
         <v>46215.80398148148</v>
       </c>
       <c r="J1028">
-        <v>2.913989319935304</v>
+        <v>2.913989319935305</v>
       </c>
       <c r="K1028">
-        <v>2.913989319935304</v>
+        <v>2.913989319935305</v>
       </c>
     </row>
     <row r="1029" spans="1:11">
@@ -38188,10 +38188,10 @@
         <v>46179.37181712963</v>
       </c>
       <c r="J1067">
-        <v>2.024166744114818</v>
+        <v>2.024166744114819</v>
       </c>
       <c r="K1067">
-        <v>2.024166744114818</v>
+        <v>2.024166744114819</v>
       </c>
     </row>
     <row r="1068" spans="1:11">
@@ -38818,10 +38818,10 @@
         <v>46208.72771990741</v>
       </c>
       <c r="J1085">
-        <v>3.991788443202278</v>
+        <v>3.991788443202279</v>
       </c>
       <c r="K1085">
-        <v>3.991788443202278</v>
+        <v>3.991788443202279</v>
       </c>
     </row>
     <row r="1086" spans="1:11">
@@ -39203,10 +39203,10 @@
         <v>46208.72771990741</v>
       </c>
       <c r="J1096">
-        <v>3.935744488851968</v>
+        <v>3.935744488851969</v>
       </c>
       <c r="K1096">
-        <v>3.935744488851968</v>
+        <v>3.935744488851969</v>
       </c>
     </row>
     <row r="1097" spans="1:11">
@@ -39518,10 +39518,10 @@
         <v>46221.81929398148</v>
       </c>
       <c r="J1105">
-        <v>4.760781741335358</v>
+        <v>4.760781741335359</v>
       </c>
       <c r="K1105">
-        <v>4.760781741335358</v>
+        <v>4.760781741335359</v>
       </c>
     </row>
     <row r="1106" spans="1:11">
@@ -39658,10 +39658,10 @@
         <v>46183.41065972222</v>
       </c>
       <c r="J1109">
-        <v>3.985120586634553</v>
+        <v>3.985120586634552</v>
       </c>
       <c r="K1109">
-        <v>3.985120586634553</v>
+        <v>3.985120586634552</v>
       </c>
     </row>
     <row r="1110" spans="1:11">
@@ -39973,10 +39973,10 @@
         <v>46183.41065972222</v>
       </c>
       <c r="J1118">
-        <v>3.985120586634553</v>
+        <v>3.985120586634552</v>
       </c>
       <c r="K1118">
-        <v>3.985120586634553</v>
+        <v>3.985120586634552</v>
       </c>
     </row>
     <row r="1119" spans="1:11">
@@ -40253,10 +40253,10 @@
         <v>46213.2546412037</v>
       </c>
       <c r="J1126">
-        <v>3.479987465329009</v>
+        <v>3.479987465329008</v>
       </c>
       <c r="K1126">
-        <v>3.479987465329009</v>
+        <v>3.479987465329008</v>
       </c>
     </row>
     <row r="1127" spans="1:11">
@@ -40323,10 +40323,10 @@
         <v>46215.80398148148</v>
       </c>
       <c r="J1128">
-        <v>2.774570331938189</v>
+        <v>2.77457033193819</v>
       </c>
       <c r="K1128">
-        <v>2.774570331938189</v>
+        <v>2.77457033193819</v>
       </c>
     </row>
     <row r="1129" spans="1:11">
@@ -40638,10 +40638,10 @@
         <v>46221.81929398148</v>
       </c>
       <c r="J1137">
-        <v>3.22733062557666</v>
+        <v>3.227330625576659</v>
       </c>
       <c r="K1137">
-        <v>3.22733062557666</v>
+        <v>3.227330625576659</v>
       </c>
     </row>
     <row r="1138" spans="1:11">
@@ -40743,10 +40743,10 @@
         <v>46177.18960648148</v>
       </c>
       <c r="J1140">
-        <v>6.663964406020221</v>
+        <v>6.663964406020222</v>
       </c>
       <c r="K1140">
-        <v>6.663964406020221</v>
+        <v>6.663964406020222</v>
       </c>
     </row>
     <row r="1141" spans="1:11">
@@ -40918,10 +40918,10 @@
         <v>46207.74719907407</v>
       </c>
       <c r="J1145">
-        <v>4.953365806861997</v>
+        <v>4.953365806861995</v>
       </c>
       <c r="K1145">
-        <v>4.953365806861997</v>
+        <v>4.953365806861995</v>
       </c>
     </row>
     <row r="1146" spans="1:11">
@@ -41058,10 +41058,10 @@
         <v>46211.28827546296</v>
       </c>
       <c r="J1149">
-        <v>3.47585071853425</v>
+        <v>3.475850718534249</v>
       </c>
       <c r="K1149">
-        <v>3.47585071853425</v>
+        <v>3.475850718534249</v>
       </c>
     </row>
     <row r="1150" spans="1:11">
@@ -41093,10 +41093,10 @@
         <v>46212.95300925926</v>
       </c>
       <c r="J1150">
-        <v>4.820711964431121</v>
+        <v>4.82071196443112</v>
       </c>
       <c r="K1150">
-        <v>4.820711964431121</v>
+        <v>4.82071196443112</v>
       </c>
     </row>
     <row r="1151" spans="1:11">
@@ -41513,10 +41513,10 @@
         <v>46216.5744675926</v>
       </c>
       <c r="J1162">
-        <v>3.028170939491921</v>
+        <v>3.028170939491922</v>
       </c>
       <c r="K1162">
-        <v>3.028170939491921</v>
+        <v>3.028170939491922</v>
       </c>
     </row>
     <row r="1163" spans="1:11">
@@ -41933,10 +41933,10 @@
         <v>46212.99814814814</v>
       </c>
       <c r="J1174">
-        <v>3.325646868976113</v>
+        <v>3.325646868976112</v>
       </c>
       <c r="K1174">
-        <v>3.325646868976113</v>
+        <v>3.325646868976112</v>
       </c>
     </row>
     <row r="1175" spans="1:11">
@@ -42073,10 +42073,10 @@
         <v>46216.5744675926</v>
       </c>
       <c r="J1178">
-        <v>3.028170939491921</v>
+        <v>3.028170939491922</v>
       </c>
       <c r="K1178">
-        <v>3.028170939491921</v>
+        <v>3.028170939491922</v>
       </c>
     </row>
     <row r="1179" spans="1:11">
@@ -43403,10 +43403,10 @@
         <v>46208.75350694444</v>
       </c>
       <c r="J1216">
-        <v>2.388617512458681</v>
+        <v>2.388617512458682</v>
       </c>
       <c r="K1216">
-        <v>2.388617512458681</v>
+        <v>2.388617512458682</v>
       </c>
     </row>
     <row r="1217" spans="1:11">
@@ -43578,10 +43578,10 @@
         <v>46213.25635416667</v>
       </c>
       <c r="J1221">
-        <v>2.86092133721335</v>
+        <v>2.860921337213349</v>
       </c>
       <c r="K1221">
-        <v>2.86092133721335</v>
+        <v>2.860921337213349</v>
       </c>
     </row>
     <row r="1222" spans="1:11">
@@ -43893,10 +43893,10 @@
         <v>46215.58039351852</v>
       </c>
       <c r="J1230">
-        <v>3.368606033305217</v>
+        <v>3.368606033305218</v>
       </c>
       <c r="K1230">
-        <v>3.368606033305217</v>
+        <v>3.368606033305218</v>
       </c>
     </row>
     <row r="1231" spans="1:11">
@@ -43928,10 +43928,10 @@
         <v>46216.57445601852</v>
       </c>
       <c r="J1231">
-        <v>3.794669474874621</v>
+        <v>3.794669474874622</v>
       </c>
       <c r="K1231">
-        <v>3.794669474874621</v>
+        <v>3.794669474874622</v>
       </c>
     </row>
     <row r="1232" spans="1:11">
@@ -44348,10 +44348,10 @@
         <v>46212.99813657408</v>
       </c>
       <c r="J1243">
-        <v>3.493946984880699</v>
+        <v>3.493946984880698</v>
       </c>
       <c r="K1243">
-        <v>3.493946984880699</v>
+        <v>3.493946984880698</v>
       </c>
     </row>
     <row r="1244" spans="1:11">
@@ -44383,10 +44383,10 @@
         <v>46213.25635416667</v>
       </c>
       <c r="J1244">
-        <v>3.760087331859638</v>
+        <v>3.760087331859639</v>
       </c>
       <c r="K1244">
-        <v>3.760087331859638</v>
+        <v>3.760087331859639</v>
       </c>
     </row>
     <row r="1245" spans="1:11">
@@ -44488,10 +44488,10 @@
         <v>46216.57445601852</v>
       </c>
       <c r="J1247">
-        <v>3.794669474874621</v>
+        <v>3.794669474874622</v>
       </c>
       <c r="K1247">
-        <v>3.794669474874621</v>
+        <v>3.794669474874622</v>
       </c>
     </row>
     <row r="1248" spans="1:11">
@@ -44803,10 +44803,10 @@
         <v>46176.68560185185</v>
       </c>
       <c r="J1256">
-        <v>2.686978651339331</v>
+        <v>2.68697865133933</v>
       </c>
       <c r="K1256">
-        <v>2.686978651339331</v>
+        <v>2.68697865133933</v>
       </c>
     </row>
     <row r="1257" spans="1:11">
@@ -45188,10 +45188,10 @@
         <v>46213.25634259259</v>
       </c>
       <c r="J1267">
-        <v>2.392717925780295</v>
+        <v>2.392717925780296</v>
       </c>
       <c r="K1267">
-        <v>2.392717925780295</v>
+        <v>2.392717925780296</v>
       </c>
     </row>
     <row r="1268" spans="1:11">
@@ -45328,10 +45328,10 @@
         <v>46181.62082175926</v>
       </c>
       <c r="J1271">
-        <v>2.036626280489694</v>
+        <v>2.036626280489693</v>
       </c>
       <c r="K1271">
-        <v>2.036626280489694</v>
+        <v>2.036626280489693</v>
       </c>
     </row>
     <row r="1272" spans="1:11">
@@ -46273,10 +46273,10 @@
         <v>46215.66931712963</v>
       </c>
       <c r="J1298">
-        <v>1.470992471229654</v>
+        <v>1.470992471229655</v>
       </c>
       <c r="K1298">
-        <v>1.470992471229654</v>
+        <v>1.470992471229655</v>
       </c>
     </row>
     <row r="1299" spans="1:11">
@@ -46343,10 +46343,10 @@
         <v>46217.74158564815</v>
       </c>
       <c r="J1300">
-        <v>1.631645397076415</v>
+        <v>1.631645397076416</v>
       </c>
       <c r="K1300">
-        <v>1.631645397076415</v>
+        <v>1.631645397076416</v>
       </c>
     </row>
     <row r="1301" spans="1:11">
@@ -46518,10 +46518,10 @@
         <v>46215.37017361111</v>
       </c>
       <c r="J1305">
-        <v>1.834287512967896</v>
+        <v>1.834287512967897</v>
       </c>
       <c r="K1305">
-        <v>1.834287512967896</v>
+        <v>1.834287512967897</v>
       </c>
     </row>
     <row r="1306" spans="1:11">
@@ -46763,10 +46763,10 @@
         <v>46215.37017361111</v>
       </c>
       <c r="J1312">
-        <v>1.520841832412492</v>
+        <v>1.520841832412491</v>
       </c>
       <c r="K1312">
-        <v>1.520841832412492</v>
+        <v>1.520841832412491</v>
       </c>
     </row>
     <row r="1313" spans="1:11">
@@ -47743,10 +47743,10 @@
         <v>46211.09550925926</v>
       </c>
       <c r="J1340">
-        <v>1.760217160848159</v>
+        <v>1.760217160848158</v>
       </c>
       <c r="K1340">
-        <v>1.760217160848159</v>
+        <v>1.760217160848158</v>
       </c>
     </row>
     <row r="1341" spans="1:11">
